--- a/data/trans_dic/P36$nada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36$nada-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no desayuna</t>
+          <t>Población que no desayuna (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,67</t>
+          <t>0,71; 4,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,41</t>
+          <t>1,85; 6,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,66</t>
+          <t>0,8; 4,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,35</t>
+          <t>0,76; 4,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,38</t>
+          <t>1,61; 6,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,95</t>
+          <t>0,31; 3,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,65</t>
+          <t>0,99; 3,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,4</t>
+          <t>1,93; 5,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,18</t>
+          <t>0,86; 3,11</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,94</t>
+          <t>2,31; 5,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,41</t>
+          <t>1,36; 4,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,74</t>
+          <t>0,6; 2,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,07</t>
+          <t>1,3; 3,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,95</t>
+          <t>0,99; 3,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,06</t>
+          <t>0,37; 2,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,33</t>
+          <t>2,11; 4,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,48</t>
+          <t>1,46; 3,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,03</t>
+          <t>0,65; 2,01</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,43</t>
+          <t>0,32; 3,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,31</t>
+          <t>0,27; 2,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,0</t>
+          <t>0,29; 3,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,56</t>
+          <t>0,57; 2,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,66</t>
+          <t>0,27; 1,67</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,03</t>
+          <t>2,13; 6,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,01</t>
+          <t>2,25; 7,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,27</t>
+          <t>1,94; 6,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,66</t>
+          <t>0,26; 2,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,78</t>
+          <t>0,28; 2,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,79</t>
+          <t>0,65; 3,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,77</t>
+          <t>1,43; 3,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,2</t>
+          <t>1,48; 4,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,24</t>
+          <t>1,55; 4,33</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,31</t>
+          <t>0,93; 5,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,15</t>
+          <t>1,39; 8,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,96</t>
+          <t>0,76; 5,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,92</t>
+          <t>0,89; 5,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,09</t>
+          <t>0,65; 3,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,49</t>
+          <t>1,58; 5,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,71</t>
+          <t>0,43; 2,85</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,92</t>
+          <t>0,31; 2,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,84</t>
+          <t>1,38; 6,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,29</t>
+          <t>1,14; 5,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,85</t>
+          <t>0,34; 3,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,39</t>
+          <t>0,35; 3,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,05</t>
+          <t>1,43; 6,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,27</t>
+          <t>0,5; 2,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,24</t>
+          <t>1,19; 4,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,79</t>
+          <t>1,94; 4,72</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,88</t>
+          <t>0,74; 2,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,79</t>
+          <t>1,88; 4,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,14</t>
+          <t>0,83; 3,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,16</t>
+          <t>0,84; 3,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,66</t>
+          <t>1,34; 3,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,42</t>
+          <t>0,15; 1,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,5</t>
+          <t>0,97; 2,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,73</t>
+          <t>1,85; 3,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,94</t>
+          <t>0,63; 1,94</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,57</t>
+          <t>0,82; 2,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,31</t>
+          <t>0,51; 2,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,74</t>
+          <t>0,77; 2,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,17</t>
+          <t>1,14; 3,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,8</t>
+          <t>0,39; 1,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,09</t>
+          <t>0,12; 1,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,53</t>
+          <t>1,18; 2,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,71</t>
+          <t>0,57; 1,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,64</t>
+          <t>0,56; 1,57</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,63</t>
+          <t>1,59; 2,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,27</t>
+          <t>2,02; 3,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,46</t>
+          <t>1,47; 2,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,03</t>
+          <t>1,17; 2,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,27</t>
+          <t>1,31; 2,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,39</t>
+          <t>0,71; 1,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,21</t>
+          <t>1,53; 2,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,57</t>
+          <t>1,8; 2,63</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,81</t>
+          <t>1,17; 1,72</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no desayuna</t>
+          <t>Población que no desayuna (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1921; 12665</t>
+          <t>1927; 12274</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5437; 18885</t>
+          <t>5455; 19424</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2068; 13686</t>
+          <t>2343; 13834</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1974; 11305</t>
+          <t>1985; 11185</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4578; 18261</t>
+          <t>4596; 18157</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1082; 11411</t>
+          <t>909; 9055</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4937; 19374</t>
+          <t>5254; 18533</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11854; 31386</t>
+          <t>11234; 29969</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4701; 18551</t>
+          <t>5028; 18109</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12215; 29226</t>
+          <t>11378; 29255</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6829; 22235</t>
+          <t>6840; 22312</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2987; 13715</t>
+          <t>2980; 13965</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7187; 20495</t>
+          <t>6534; 19295</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5190; 20620</t>
+          <t>5143; 19616</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1932; 10766</t>
+          <t>1938; 10747</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21449; 43111</t>
+          <t>21040; 43945</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14953; 35727</t>
+          <t>14959; 37668</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6059; 20733</t>
+          <t>6662; 20564</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3984</t>
+          <t>0; 5040</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1024; 11070</t>
+          <t>1036; 11039</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>854; 7365</t>
+          <t>849; 7211</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4027</t>
+          <t>0; 5000</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>980; 10244</t>
+          <t>976; 10925</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5885</t>
+          <t>0; 6304</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6229</t>
+          <t>0; 6614</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3362; 16971</t>
+          <t>3814; 16311</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1780; 10896</t>
+          <t>1773; 10933</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6948; 21581</t>
+          <t>7622; 22374</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7764; 26157</t>
+          <t>8405; 26823</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7655; 23212</t>
+          <t>7170; 25281</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>943; 9895</t>
+          <t>980; 9624</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1090; 10799</t>
+          <t>1087; 10746</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2756; 14666</t>
+          <t>2501; 15114</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10852; 27501</t>
+          <t>10438; 26437</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11383; 32018</t>
+          <t>11292; 32440</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12501; 32119</t>
+          <t>11760; 32811</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1791; 10755</t>
+          <t>1881; 11204</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3133; 17320</t>
+          <t>2948; 18409</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>990; 10480</t>
+          <t>1610; 11011</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5988</t>
+          <t>0; 6041</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1890; 10812</t>
+          <t>1945; 11061</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3874</t>
+          <t>0; 4960</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2647; 12641</t>
+          <t>2642; 13589</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6128; 23730</t>
+          <t>6848; 24184</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1837; 11643</t>
+          <t>1861; 12266</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>852; 7900</t>
+          <t>845; 7686</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4012; 18754</t>
+          <t>3779; 18411</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2984; 13914</t>
+          <t>2987; 13868</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>942; 7922</t>
+          <t>940; 8568</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>979; 9445</t>
+          <t>990; 9573</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3908; 16458</t>
+          <t>3899; 17033</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2740; 12460</t>
+          <t>2742; 13228</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6651; 23420</t>
+          <t>6582; 23389</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9217; 25645</t>
+          <t>10387; 25239</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4581; 17667</t>
+          <t>4541; 17036</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12008; 31772</t>
+          <t>12459; 31862</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5019; 20536</t>
+          <t>5415; 22161</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5769; 20098</t>
+          <t>5347; 20623</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9042; 25418</t>
+          <t>9306; 26067</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1017; 9778</t>
+          <t>1024; 10988</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12123; 31252</t>
+          <t>12122; 30957</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>25721; 50627</t>
+          <t>25152; 50474</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8187; 26028</t>
+          <t>8418; 26058</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5687; 19084</t>
+          <t>6080; 20612</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3967; 17965</t>
+          <t>3957; 18381</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6081; 21322</t>
+          <t>6025; 21658</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9430; 24867</t>
+          <t>8967; 24520</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3242; 14759</t>
+          <t>3182; 14961</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>981; 8984</t>
+          <t>981; 8892</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17951; 38682</t>
+          <t>18058; 38446</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9333; 27364</t>
+          <t>9165; 26076</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8902; 26385</t>
+          <t>9006; 25122</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>53617; 86118</t>
+          <t>52059; 85648</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>71506; 111914</t>
+          <t>68931; 110026</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49617; 83495</t>
+          <t>49710; 84215</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40235; 68593</t>
+          <t>39420; 69792</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>46793; 80458</t>
+          <t>46694; 78507</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25658; 49321</t>
+          <t>25221; 49154</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>100811; 146599</t>
+          <t>101491; 145377</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>126625; 179043</t>
+          <t>125629; 183500</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>80945; 125550</t>
+          <t>81086; 119229</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$nada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36$nada-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,53</t>
+          <t>0,71; 4,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,59</t>
+          <t>1,78; 6,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,71</t>
+          <t>0,8; 4,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,31</t>
+          <t>0,75; 4,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,34</t>
+          <t>1,52; 6,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,14</t>
+          <t>0,37; 3,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,49</t>
+          <t>0,96; 3,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,16</t>
+          <t>2,08; 5,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,11</t>
+          <t>0,82; 3,13</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,95</t>
+          <t>2,48; 5,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,79</t>
+          <t>0,58; 2,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,83</t>
+          <t>1,44; 4,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,76</t>
+          <t>1,15; 3,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,05</t>
+          <t>0,37; 2,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,41</t>
+          <t>2,17; 4,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,67</t>
+          <t>1,45; 3,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,01</t>
+          <t>0,6; 1,91</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,42</t>
+          <t>0,32; 3,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,26</t>
+          <t>0,27; 2,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,2</t>
+          <t>0,29; 3,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,46</t>
+          <t>0,55; 2,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,67</t>
+          <t>0,17; 1,52</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,26</t>
+          <t>2,04; 6,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,19</t>
+          <t>2,18; 7,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,83</t>
+          <t>2,04; 6,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,59</t>
+          <t>0,31; 2,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,76</t>
+          <t>0,28; 2,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,9</t>
+          <t>0,64; 3,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,63</t>
+          <t>1,47; 3,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,26</t>
+          <t>1,55; 4,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,33</t>
+          <t>1,74; 4,25</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,54</t>
+          <t>0,91; 5,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,66</t>
+          <t>1,36; 7,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,21</t>
+          <t>0,48; 5,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,04</t>
+          <t>0,9; 4,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,32</t>
+          <t>0,65; 3,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,6</t>
+          <t>1,6; 5,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,85</t>
+          <t>0,44; 2,91</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,84</t>
+          <t>0,31; 3,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,72</t>
+          <t>1,4; 7,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,27</t>
+          <t>1,14; 5,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,08</t>
+          <t>0,34; 3,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,43</t>
+          <t>0,32; 3,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,26</t>
+          <t>1,7; 6,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,41</t>
+          <t>0,49; 2,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,23</t>
+          <t>1,15; 4,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,72</t>
+          <t>1,74; 4,69</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,78</t>
+          <t>0,75; 2,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,81</t>
+          <t>1,88; 4,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,38</t>
+          <t>0,82; 3,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,24</t>
+          <t>0,95; 3,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,76</t>
+          <t>1,36; 3,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,59</t>
+          <t>0,15; 1,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,48</t>
+          <t>1,0; 2,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,72</t>
+          <t>1,78; 3,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,94</t>
+          <t>0,68; 2,08</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,77</t>
+          <t>0,76; 2,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,37</t>
+          <t>0,53; 2,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,78</t>
+          <t>0,77; 2,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,13</t>
+          <t>1,1; 3,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,82</t>
+          <t>0,38; 1,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,08</t>
+          <t>0,12; 1,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,52</t>
+          <t>1,19; 2,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,63</t>
+          <t>0,58; 1,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,57</t>
+          <t>0,57; 1,59</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,62</t>
+          <t>1,6; 2,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,22</t>
+          <t>2,09; 3,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,48</t>
+          <t>1,47; 2,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,07</t>
+          <t>1,22; 2,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,21</t>
+          <t>1,32; 2,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,39</t>
+          <t>0,7; 1,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,19</t>
+          <t>1,53; 2,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,63</t>
+          <t>1,83; 2,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,72</t>
+          <t>1,17; 1,74</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1927; 12274</t>
+          <t>1936; 12614</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5455; 19424</t>
+          <t>5245; 18567</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2343; 13834</t>
+          <t>2357; 13670</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1985; 11185</t>
+          <t>1960; 11604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4596; 18157</t>
+          <t>4352; 18178</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>909; 9055</t>
+          <t>1059; 10069</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5254; 18533</t>
+          <t>5089; 18612</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11234; 29969</t>
+          <t>12063; 32455</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5028; 18109</t>
+          <t>4787; 18247</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11378; 29255</t>
+          <t>12205; 29264</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6840; 22312</t>
+          <t>6871; 22320</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2980; 13965</t>
+          <t>2911; 13168</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6534; 19295</t>
+          <t>7239; 21052</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5143; 19616</t>
+          <t>5994; 19501</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1938; 10747</t>
+          <t>1944; 10789</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21040; 43945</t>
+          <t>21572; 43130</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14959; 37668</t>
+          <t>14896; 35089</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6662; 20564</t>
+          <t>6152; 19526</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5040</t>
+          <t>0; 4460</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1036; 11039</t>
+          <t>1029; 10424</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>849; 7211</t>
+          <t>858; 7382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5000</t>
+          <t>0; 5028</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>976; 10925</t>
+          <t>981; 10985</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6304</t>
+          <t>0; 6271</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6614</t>
+          <t>0; 6488</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3814; 16311</t>
+          <t>3678; 16696</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1773; 10933</t>
+          <t>1107; 9937</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7622; 22374</t>
+          <t>7313; 22814</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8405; 26823</t>
+          <t>8133; 27326</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7170; 25281</t>
+          <t>7533; 23530</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>980; 9624</t>
+          <t>1144; 9589</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1087; 10746</t>
+          <t>1091; 10578</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2501; 15114</t>
+          <t>2472; 14129</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10438; 26437</t>
+          <t>10752; 27292</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11292; 32440</t>
+          <t>11771; 32764</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11760; 32811</t>
+          <t>13209; 32190</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1881; 11204</t>
+          <t>1844; 10928</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2948; 18409</t>
+          <t>2889; 16385</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1610; 11011</t>
+          <t>1003; 11191</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 6041</t>
+          <t>0; 5195</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1945; 11061</t>
+          <t>1981; 10445</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4960</t>
+          <t>0; 4154</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2642; 13589</t>
+          <t>2639; 12571</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6848; 24184</t>
+          <t>6900; 23268</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1861; 12266</t>
+          <t>1875; 12494</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>845; 7686</t>
+          <t>848; 8430</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3779; 18411</t>
+          <t>3843; 19561</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2987; 13868</t>
+          <t>3008; 13816</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>940; 8568</t>
+          <t>948; 9162</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>990; 9573</t>
+          <t>903; 8624</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3899; 17033</t>
+          <t>4625; 17244</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2742; 13228</t>
+          <t>2712; 13057</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6582; 23389</t>
+          <t>6350; 22652</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10387; 25239</t>
+          <t>9326; 25092</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4541; 17036</t>
+          <t>4579; 18159</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12459; 31862</t>
+          <t>12474; 32072</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5415; 22161</t>
+          <t>5392; 20858</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5347; 20623</t>
+          <t>6021; 21377</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9306; 26067</t>
+          <t>9403; 27099</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1024; 10988</t>
+          <t>1058; 9927</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12122; 30957</t>
+          <t>12474; 31209</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>25152; 50474</t>
+          <t>24139; 51094</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8418; 26058</t>
+          <t>9092; 27962</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6080; 20612</t>
+          <t>5628; 18297</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3957; 18381</t>
+          <t>4098; 18591</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6025; 21658</t>
+          <t>6016; 21272</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8967; 24520</t>
+          <t>8595; 23711</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3182; 14961</t>
+          <t>3146; 14793</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>981; 8892</t>
+          <t>987; 9868</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18058; 38446</t>
+          <t>18123; 38025</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9165; 26076</t>
+          <t>9319; 27095</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9006; 25122</t>
+          <t>9081; 25446</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>52059; 85648</t>
+          <t>52434; 84976</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>68931; 110026</t>
+          <t>71506; 112203</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49710; 84215</t>
+          <t>49934; 82559</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39420; 69792</t>
+          <t>41150; 72259</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>46694; 78507</t>
+          <t>47040; 79044</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25221; 49154</t>
+          <t>24758; 48971</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>101491; 145377</t>
+          <t>101631; 144151</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>125629; 183500</t>
+          <t>127785; 179095</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>81086; 119229</t>
+          <t>81435; 120669</t>
         </is>
       </c>
     </row>
